--- a/docs/policy-governance-events.xlsx
+++ b/docs/policy-governance-events.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="38">
   <si>
     <t>event_id</t>
   </si>
@@ -108,6 +108,27 @@
   </si>
   <si>
     <t>afp-tools/src/main/java/com/upland/connect/afp/tools/StateDatabaseTool.java|build.gradle|preview/version-control-ledger.json|preview/state/project-state.sqlite</t>
+  </si>
+  <si>
+    <t>docs/policy-governance-events.csv|docs/policy-governance-events.xlsx|build.gradle|pm-tools/src/main/java/com/upland/connect/pm/tools/PolicyGovernanceWorkbookUpdater.java</t>
+  </si>
+  <si>
+    <t>AI-POLICY.md|build.gradle|pm-tools/src/main/java/com/upland/connect/pm/tools/StateDatabaseTool.java|preview/governance-alerts.json</t>
+  </si>
+  <si>
+    <t>pm-tools/src/main/java/com/upland/connect/pm/tools/StateDatabaseTool.java|build.gradle|preview/version-control-ledger.json|preview/state/project-state.sqlite</t>
+  </si>
+  <si>
+    <t>pm-tools/src/main/java/com/upland/connect/pm/tools/StateDatabaseTool.java|build.gradle|preview/version-control-ledger.json|project/state/project-state.sqlite</t>
+  </si>
+  <si>
+    <t>AI-POLICY.md|docs/issues-log.csv|SESSION_CHANGELOG.md|pm/checkpoints/20260218T214353Z-0.2.0-beta.1-policy-first-principles-governance-fix</t>
+  </si>
+  <si>
+    <t>AI-POLICY.md|build.gradle|pm-tools/src/main/java/com/upland/connect/pm/tools/StateDatabaseTool.java|pm/reports/governance-alerts.json</t>
+  </si>
+  <si>
+    <t>pm-tools/src/main/java/com/upland/connect/pm/tools/StateDatabaseTool.java|build.gradle|pm/reports/version-control-ledger.json|pm/state/project-state.sqlite</t>
   </si>
 </sst>
 </file>
@@ -207,7 +228,7 @@
         <v>15</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>17</v>
@@ -236,7 +257,7 @@
         <v>21</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>17</v>
@@ -265,7 +286,7 @@
         <v>26</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>17</v>
@@ -294,7 +315,7 @@
         <v>29</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>17</v>

--- a/docs/policy-governance-events.xlsx
+++ b/docs/policy-governance-events.xlsx
@@ -9,13 +9,13 @@
     <sheet name="Governance Events" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Governance Events'!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Governance Events'!$A$1:$I$6</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="46">
   <si>
     <t>event_id</t>
   </si>
@@ -138,6 +138,21 @@
   </si>
   <si>
     <t>pm-tools/src/main/java/solutions/pointzero/symphony/pm/tools/StateDatabaseTool.java|build.gradle|pm/reports/version-control-ledger.json|pm/state/project-state.sqlite</t>
+  </si>
+  <si>
+    <t>GOV-2026-02-19-001</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>20260219T194452Z-0.2.0-beta.1-checkpoint</t>
+  </si>
+  <si>
+    <t>Executed controlled SQL managed-file delete-and-remanifest drill with rollback checkpoint and reconstruction/quality verification.</t>
+  </si>
+  <si>
+    <t>pm/state/managed-delete-manifest.txt|pm/reports/remanifest-drill.json|pm/checkpoints/20260219T194452Z-0.2.0-beta.1-checkpoint|build.gradle</t>
   </si>
 </sst>
 </file>
@@ -182,7 +197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -330,8 +345,37 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/docs/policy-governance-events.xlsx
+++ b/docs/policy-governance-events.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="46">
   <si>
     <t>event_id</t>
   </si>
